--- a/figures/Figure3/data/melt_inclusions/Fogo_Data.xlsx
+++ b/figures/Figure3/data/melt_inclusions/Fogo_Data.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiacovino/PythonGit/EoV_CH2-2/figures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiacovino/PythonGit/EoV_CH2-2/figures/Figure3/data/melt_inclusions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CA9888-C308-0A42-B3CA-6362A1089A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEC09E3-E920-264B-A530-23F0EDD0B986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12620" yWindow="29360" windowWidth="29920" windowHeight="18780" xr2:uid="{55660F85-C404-C848-8A24-B7699FD5DC80}"/>
+    <workbookView xWindow="15180" yWindow="36320" windowWidth="29920" windowHeight="18780" activeTab="1" xr2:uid="{55660F85-C404-C848-8A24-B7699FD5DC80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Citations" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="94">
   <si>
     <t>FG04-1-MI1</t>
   </si>
@@ -309,13 +310,66 @@
   </si>
   <si>
     <t>Fogo</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>DeVitre et al. 2023</t>
+  </si>
+  <si>
+    <r>
+      <t>DeVitre, C. L. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>et al.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> Oceanic intraplate explosive eruptions fed directly from the mantle. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PNAS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (2023).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -331,17 +385,45 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -364,11 +446,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -683,13 +767,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7442C20-FBA8-E748-8797-F7AAD5819D24}">
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
@@ -697,3384 +782,3638 @@
         <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="3">
         <v>44.93</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="3">
         <v>3.78</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="3">
         <v>14.25</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="3">
         <v>12.9</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="3">
         <v>0.31</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="3">
         <v>5.88</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="3">
         <v>7.93</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="3">
         <v>4.24</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="3">
         <v>2.58</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="3">
         <v>1.23</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="2">
         <v>1.637</v>
       </c>
-      <c r="N2" s="3">
+      <c r="O2" s="2">
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="3">
         <v>42.51</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="3">
         <v>3.18</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="3">
         <v>14.5</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="3">
         <v>12.9</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="3">
         <v>0.2</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="3">
         <v>6.43</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="3">
         <v>10.95</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="3">
         <v>3.58</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="3">
         <v>2.2599999999999998</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="3">
         <v>0.88</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="2">
         <v>2.23</v>
       </c>
-      <c r="N3" s="3">
+      <c r="O3" s="2">
         <v>0.29699999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="3">
         <v>41.34</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="3">
         <v>4.1500000000000004</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="3">
         <v>13.92</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="3">
         <v>12.9</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="3">
         <v>0.27</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="3">
         <v>6.11</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="3">
         <v>12.21</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="3">
         <v>3.67</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="3">
         <v>1.76</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="3">
         <v>0.92</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="2">
         <v>2.41</v>
       </c>
-      <c r="N4" s="3">
+      <c r="O4" s="2">
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="B5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3">
         <v>44.72</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="3">
         <v>2.8</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="3">
         <v>14.75</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="3">
         <v>13</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="3">
         <v>0.18</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="3">
         <v>6.2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="3">
         <v>8.83</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="3">
         <v>4.16</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="3">
         <v>2.39</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="3">
         <v>0.91</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="2">
         <v>1.7969999999999999</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="2">
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="B6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="3">
         <v>45.86</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="3">
         <v>2.83</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="3">
         <v>14.45</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="3">
         <v>13</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="3">
         <v>0.16</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="3">
         <v>7.07</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="3">
         <v>8.93</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="3">
         <v>3.25</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="3">
         <v>2.25</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="3">
         <v>0.86</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="2">
         <v>1.111</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="2">
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="B7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="3">
         <v>44.18</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="3">
         <v>2.95</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="3">
         <v>14.93</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="3">
         <v>13</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="3">
         <v>0.21</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="3">
         <v>6.3</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="3">
         <v>8.83</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="3">
         <v>4</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="3">
         <v>2.67</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="3">
         <v>1.1299999999999999</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="2">
         <v>1.5449999999999999</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="2">
         <v>0.218</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="3">
         <v>45.8</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="3">
         <v>1.69</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="3">
         <v>12.96</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="3">
         <v>12.9</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="3">
         <v>0.11</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="3">
         <v>11.66</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="3">
         <v>6.56</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="3">
         <v>3.29</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="3">
         <v>2.99</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="3">
         <v>0.09</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="2">
         <v>1.6459999999999999</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="2">
         <v>0.104</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="B9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="3">
         <v>42.05</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="3">
         <v>3.35</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="3">
         <v>13.59</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="3">
         <v>12.9</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="3">
         <v>0.19</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="3">
         <v>6.8</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="3">
         <v>11.92</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="3">
         <v>3.37</v>
       </c>
-      <c r="K9" s="2">
+      <c r="L9" s="3">
         <v>2.11</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="3">
         <v>0.83</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="2">
         <v>2.5289999999999999</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="2">
         <v>0.44700000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="2">
+      <c r="B10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="3">
         <v>42.36</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="3">
         <v>3.35</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="3">
         <v>13.82</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="3">
         <v>12.9</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="3">
         <v>0.21</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="3">
         <v>6.25</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="3">
         <v>11.05</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="3">
         <v>3.9</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="3">
         <v>2.1</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="3">
         <v>0.92</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="2">
         <v>2.7309999999999999</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="2">
         <v>0.32700000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="3">
         <v>42.32</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="3">
         <v>3.69</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="3">
         <v>14.62</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="3">
         <v>12.9</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="3">
         <v>0.2</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="3">
         <v>6.08</v>
       </c>
-      <c r="I11" s="2">
+      <c r="J11" s="3">
         <v>11.17</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="3">
         <v>3.36</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="3">
         <v>2.36</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="3">
         <v>1.01</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="2">
         <v>1.946</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="2">
         <v>0.27</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="3">
         <v>44</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="3">
         <v>2.85</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="3">
         <v>13.77</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="3">
         <v>12.9</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="3">
         <v>0.19</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="3">
         <v>5.46</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="3">
         <v>12.79</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="3">
         <v>3.24</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="3">
         <v>2.2200000000000002</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="3">
         <v>0.99</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="2">
         <v>1.224</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="2">
         <v>0.36599999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="B13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="3">
         <v>42.42</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="3">
         <v>3.61</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="3">
         <v>14.14</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="3">
         <v>12.9</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="3">
         <v>0.23</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="3">
         <v>6.24</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="3">
         <v>11.47</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="3">
         <v>3.43</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="3">
         <v>1.98</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="3">
         <v>0.75</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="2">
         <v>2.4750000000000001</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="2">
         <v>0.36599999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="3">
         <v>42.43</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="3">
         <v>3.35</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="3">
         <v>14.06</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="3">
         <v>12.9</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="3">
         <v>0.18</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="3">
         <v>7.05</v>
       </c>
-      <c r="I14" s="2">
+      <c r="J14" s="3">
         <v>11.58</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="3">
         <v>3.47</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="3">
         <v>2.14</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="3">
         <v>0.73</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="2">
         <v>1.728</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="2">
         <v>0.437</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="3">
         <v>42.19</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="3">
         <v>3.64</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="3">
         <v>14.24</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="3">
         <v>12.9</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="3">
         <v>0.16</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="3">
         <v>6.85</v>
       </c>
-      <c r="I15" s="2">
+      <c r="J15" s="3">
         <v>12.74</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="3">
         <v>3.29</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="3">
         <v>0.78</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="2">
         <v>0.80100000000000005</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="2">
         <v>0.30099999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="3">
         <v>42.48</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="3">
         <v>3.43</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="3">
         <v>13.95</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="3">
         <v>12.9</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="3">
         <v>0.21</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="3">
         <v>6.94</v>
       </c>
-      <c r="I16" s="2">
+      <c r="J16" s="3">
         <v>11.55</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="3">
         <v>3.09</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="3">
         <v>0.63</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="2">
         <v>2.4359999999999999</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="2">
         <v>0.442</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="3">
         <v>42.95</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="3">
         <v>2.89</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="3">
         <v>15.02</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="3">
         <v>12.9</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="3">
         <v>0.23</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="3">
         <v>6.77</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="3">
         <v>11.88</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="3">
         <v>3.15</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="3">
         <v>2.0099999999999998</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="3">
         <v>0.66</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="2">
         <v>1.18</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="2">
         <v>0.38600000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="3">
         <v>45.64</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="3">
         <v>2.97</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="3">
         <v>15.09</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="3">
         <v>12.9</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="3">
         <v>0.26</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="3">
         <v>5.79</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="3">
         <v>8.5</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="3">
         <v>4.22</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="3">
         <v>2.33</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="3">
         <v>0.73</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="2">
         <v>1.246</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="2">
         <v>0.187</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="3">
         <v>47.7</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="3">
         <v>2.3199999999999998</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="3">
         <v>15.16</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="3">
         <v>12.9</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="3">
         <v>0.24</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="3">
         <v>5.39</v>
       </c>
-      <c r="I19" s="2">
+      <c r="J19" s="3">
         <v>6.54</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="3">
         <v>4.68</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="3">
         <v>2.76</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="3">
         <v>1.03</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="2">
         <v>0.95399999999999996</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="2">
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="B20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="3">
         <v>46.32</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="3">
         <v>2.85</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="3">
         <v>14.93</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="3">
         <v>12.9</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="3">
         <v>0.24</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="3">
         <v>5.16</v>
       </c>
-      <c r="I20" s="2">
+      <c r="J20" s="3">
         <v>7.95</v>
       </c>
-      <c r="J20" s="2">
+      <c r="K20" s="3">
         <v>4.37</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="3">
         <v>2.69</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="3">
         <v>1.1599999999999999</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="2">
         <v>1.0720000000000001</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="2">
         <v>0.13800000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="B21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="3">
         <v>46.59</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="3">
         <v>2.76</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="3">
         <v>13.76</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="3">
         <v>12.9</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="3">
         <v>0.2</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="3">
         <v>5.66</v>
       </c>
-      <c r="I21" s="2">
+      <c r="J21" s="3">
         <v>10.1</v>
       </c>
-      <c r="J21" s="2">
+      <c r="K21" s="3">
         <v>3.85</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="3">
         <v>2.54</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="3">
         <v>0.68</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="2">
         <v>0.61</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="2">
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="2">
+      <c r="B22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="3">
         <v>44.31</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="3">
         <v>3.23</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="3">
         <v>13.55</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="3">
         <v>12.9</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="3">
         <v>0.15</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="3">
         <v>6.72</v>
       </c>
-      <c r="I22" s="2">
+      <c r="J22" s="3">
         <v>11.24</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="3">
         <v>3.28</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="3">
         <v>2.29</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="3">
         <v>0.9</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="2">
         <v>1.0589999999999999</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="2">
         <v>0.27600000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="3">
         <v>49.24</v>
       </c>
-      <c r="D23" s="2">
+      <c r="E23" s="3">
         <v>2.58</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="3">
         <v>14.43</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="3">
         <v>12.9</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23" s="3">
         <v>0.21</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="3">
         <v>5.76</v>
       </c>
-      <c r="I23" s="2">
+      <c r="J23" s="3">
         <v>5.3</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="3">
         <v>4.49</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="3">
         <v>2.91</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="3">
         <v>0.83</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="2">
         <v>1.0089999999999999</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="2">
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="3">
         <v>44.89</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="3">
         <v>3.06</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" s="3">
         <v>13.39</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="3">
         <v>12.9</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="3">
         <v>0.23</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="3">
         <v>5.79</v>
       </c>
-      <c r="I24" s="2">
+      <c r="J24" s="3">
         <v>10.73</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="3">
         <v>3.96</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="3">
         <v>2.21</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="3">
         <v>0.92</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="2">
         <v>1.5529999999999999</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="2">
         <v>0.155</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="3">
         <v>44.48</v>
       </c>
-      <c r="D25" s="2">
+      <c r="E25" s="3">
         <v>3.16</v>
       </c>
-      <c r="E25" s="2">
+      <c r="F25" s="3">
         <v>13.06</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="3">
         <v>12.9</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25" s="3">
         <v>0.22</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="3">
         <v>5.77</v>
       </c>
-      <c r="I25" s="2">
+      <c r="J25" s="3">
         <v>10.81</v>
       </c>
-      <c r="J25" s="2">
+      <c r="K25" s="3">
         <v>3.83</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="3">
         <v>2.33</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="3">
         <v>1.03</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="2">
         <v>2.0539999999999998</v>
       </c>
-      <c r="N25" s="3">
+      <c r="O25" s="2">
         <v>0.16400000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="3">
         <v>43.65</v>
       </c>
-      <c r="D26" s="2">
+      <c r="E26" s="3">
         <v>3.49</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F26" s="3">
         <v>13.51</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="3">
         <v>12.9</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26" s="3">
         <v>0.21</v>
       </c>
-      <c r="H26" s="2">
+      <c r="I26" s="3">
         <v>5.75</v>
       </c>
-      <c r="I26" s="2">
+      <c r="J26" s="3">
         <v>11.24</v>
       </c>
-      <c r="J26" s="2">
+      <c r="K26" s="3">
         <v>3.44</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="3">
         <v>2.2599999999999998</v>
       </c>
-      <c r="L26" s="2">
+      <c r="M26" s="3">
         <v>0.91</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="2">
         <v>2.298</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="2">
         <v>0.27</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="3">
         <v>46.87</v>
       </c>
-      <c r="D27" s="2">
+      <c r="E27" s="3">
         <v>2.9</v>
       </c>
-      <c r="E27" s="2">
+      <c r="F27" s="3">
         <v>14.24</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="3">
         <v>12.9</v>
       </c>
-      <c r="G27" s="2">
+      <c r="H27" s="3">
         <v>0.27</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="3">
         <v>5.33</v>
       </c>
-      <c r="I27" s="2">
+      <c r="J27" s="3">
         <v>7.46</v>
       </c>
-      <c r="J27" s="2">
+      <c r="K27" s="3">
         <v>4.74</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="3">
         <v>2.7</v>
       </c>
-      <c r="L27" s="2">
+      <c r="M27" s="3">
         <v>1.17</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="2">
         <v>1.0660000000000001</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="2">
         <v>0.11</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="3">
         <v>45.18</v>
       </c>
-      <c r="D28" s="2">
+      <c r="E28" s="3">
         <v>2.4700000000000002</v>
       </c>
-      <c r="E28" s="2">
+      <c r="F28" s="3">
         <v>15.52</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="3">
         <v>12.9</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H28" s="3">
         <v>0.2</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="3">
         <v>6.09</v>
       </c>
-      <c r="I28" s="2">
+      <c r="J28" s="3">
         <v>6.51</v>
       </c>
-      <c r="J28" s="2">
+      <c r="K28" s="3">
         <v>5.15</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="3">
         <v>3.02</v>
       </c>
-      <c r="L28" s="2">
+      <c r="M28" s="3">
         <v>1.24</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="2">
         <v>1.25</v>
       </c>
-      <c r="N28" s="3">
+      <c r="O28" s="2">
         <v>0.156</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="3">
         <v>42.59</v>
       </c>
-      <c r="D29" s="2">
+      <c r="E29" s="3">
         <v>3.56</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" s="3">
         <v>13.21</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="3">
         <v>12.9</v>
       </c>
-      <c r="G29" s="2">
+      <c r="H29" s="3">
         <v>0.18</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="3">
         <v>6.8</v>
       </c>
-      <c r="I29" s="2">
+      <c r="J29" s="3">
         <v>11.96</v>
       </c>
-      <c r="J29" s="2">
+      <c r="K29" s="3">
         <v>3.41</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="3">
         <v>2.13</v>
       </c>
-      <c r="L29" s="2">
+      <c r="M29" s="3">
         <v>0.85</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="2">
         <v>2.0150000000000001</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="2">
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="3">
         <v>41.7</v>
       </c>
-      <c r="D30" s="2">
+      <c r="E30" s="3">
         <v>3.73</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="3">
         <v>13.5</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="3">
         <v>12.9</v>
       </c>
-      <c r="G30" s="2">
+      <c r="H30" s="3">
         <v>0.22</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="3">
         <v>6.62</v>
       </c>
-      <c r="I30" s="2">
+      <c r="J30" s="3">
         <v>11.9</v>
       </c>
-      <c r="J30" s="2">
+      <c r="K30" s="3">
         <v>3.49</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="3">
         <v>2.21</v>
       </c>
-      <c r="L30" s="2">
+      <c r="M30" s="3">
         <v>0.9</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="2">
         <v>2.4020000000000001</v>
       </c>
-      <c r="N30" s="3">
+      <c r="O30" s="2">
         <v>0.44500000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="2">
+      <c r="B31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="3">
         <v>43.05</v>
       </c>
-      <c r="D31" s="2">
+      <c r="E31" s="3">
         <v>3.4</v>
       </c>
-      <c r="E31" s="2">
+      <c r="F31" s="3">
         <v>13.64</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="3">
         <v>12.9</v>
       </c>
-      <c r="G31" s="2">
+      <c r="H31" s="3">
         <v>0.19</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="3">
         <v>6.77</v>
       </c>
-      <c r="I31" s="2">
+      <c r="J31" s="3">
         <v>11.73</v>
       </c>
-      <c r="J31" s="2">
+      <c r="K31" s="3">
         <v>3.99</v>
       </c>
-      <c r="K31" s="2">
+      <c r="L31" s="3">
         <v>1.92</v>
       </c>
-      <c r="L31" s="2">
+      <c r="M31" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="2">
         <v>1.6950000000000001</v>
       </c>
-      <c r="N31" s="3">
+      <c r="O31" s="2">
         <v>0.61</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="B32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="3">
         <v>41.8</v>
       </c>
-      <c r="D32" s="2">
+      <c r="E32" s="3">
         <v>3.49</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F32" s="3">
         <v>14.23</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="3">
         <v>12.9</v>
       </c>
-      <c r="G32" s="2">
+      <c r="H32" s="3">
         <v>0.17</v>
       </c>
-      <c r="H32" s="2">
+      <c r="I32" s="3">
         <v>6.79</v>
       </c>
-      <c r="I32" s="2">
+      <c r="J32" s="3">
         <v>11.63</v>
       </c>
-      <c r="J32" s="2">
+      <c r="K32" s="3">
         <v>3.91</v>
       </c>
-      <c r="K32" s="2">
+      <c r="L32" s="3">
         <v>2.2799999999999998</v>
       </c>
-      <c r="L32" s="2">
+      <c r="M32" s="3">
         <v>0.88</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="2">
         <v>1.522</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="2">
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="B33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="3">
         <v>41.79</v>
       </c>
-      <c r="D33" s="2">
+      <c r="E33" s="3">
         <v>3.76</v>
       </c>
-      <c r="E33" s="2">
+      <c r="F33" s="3">
         <v>13.92</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="3">
         <v>13</v>
       </c>
-      <c r="G33" s="2">
+      <c r="H33" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="3">
         <v>5.68</v>
       </c>
-      <c r="I33" s="2">
+      <c r="J33" s="3">
         <v>12.74</v>
       </c>
-      <c r="J33" s="2">
+      <c r="K33" s="3">
         <v>3.84</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="3">
         <v>2.31</v>
       </c>
-      <c r="L33" s="2">
+      <c r="M33" s="3">
         <v>0.94</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="2">
         <v>1.57</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="2">
         <v>0.38400000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="2">
+      <c r="B34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="3">
         <v>44.86</v>
       </c>
-      <c r="D34" s="2">
+      <c r="E34" s="3">
         <v>3.18</v>
       </c>
-      <c r="E34" s="2">
+      <c r="F34" s="3">
         <v>14.27</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="3">
         <v>12.9</v>
       </c>
-      <c r="G34" s="2">
+      <c r="H34" s="3">
         <v>0.22</v>
       </c>
-      <c r="H34" s="2">
+      <c r="I34" s="3">
         <v>5.59</v>
       </c>
-      <c r="I34" s="2">
+      <c r="J34" s="3">
         <v>9.5299999999999994</v>
       </c>
-      <c r="J34" s="2">
+      <c r="K34" s="3">
         <v>4.38</v>
       </c>
-      <c r="K34" s="2">
+      <c r="L34" s="3">
         <v>2.11</v>
       </c>
-      <c r="L34" s="2">
+      <c r="M34" s="3">
         <v>0.72</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="2">
         <v>1.766</v>
       </c>
-      <c r="N34" s="3">
+      <c r="O34" s="2">
         <v>0.192</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" s="2">
+      <c r="B35" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="3">
         <v>45.47</v>
       </c>
-      <c r="D35" s="2">
+      <c r="E35" s="3">
         <v>2.4300000000000002</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" s="3">
         <v>15.08</v>
       </c>
-      <c r="F35" s="2">
+      <c r="G35" s="3">
         <v>12.9</v>
       </c>
-      <c r="G35" s="2">
+      <c r="H35" s="3">
         <v>0.23</v>
       </c>
-      <c r="H35" s="2">
+      <c r="I35" s="3">
         <v>6.31</v>
       </c>
-      <c r="I35" s="2">
+      <c r="J35" s="3">
         <v>7.46</v>
       </c>
-      <c r="J35" s="2">
+      <c r="K35" s="3">
         <v>4.6100000000000003</v>
       </c>
-      <c r="K35" s="2">
+      <c r="L35" s="3">
         <v>2.74</v>
       </c>
-      <c r="L35" s="2">
+      <c r="M35" s="3">
         <v>1.19</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="2">
         <v>1.135</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="2">
         <v>0.14099999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="2">
+      <c r="B36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="3">
         <v>43.48</v>
       </c>
-      <c r="D36" s="2">
+      <c r="E36" s="3">
         <v>3.44</v>
       </c>
-      <c r="E36" s="2">
+      <c r="F36" s="3">
         <v>14.15</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G36" s="3">
         <v>12.9</v>
       </c>
-      <c r="G36" s="2">
+      <c r="H36" s="3">
         <v>0.22</v>
       </c>
-      <c r="H36" s="2">
+      <c r="I36" s="3">
         <v>6.78</v>
       </c>
-      <c r="I36" s="2">
+      <c r="J36" s="3">
         <v>10.19</v>
       </c>
-      <c r="J36" s="2">
+      <c r="K36" s="3">
         <v>3.31</v>
       </c>
-      <c r="K36" s="2">
+      <c r="L36" s="3">
         <v>2.66</v>
       </c>
-      <c r="L36" s="2">
+      <c r="M36" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="M36" s="3">
+      <c r="N36" s="2">
         <v>1.375</v>
       </c>
-      <c r="N36" s="3">
+      <c r="O36" s="2">
         <v>0.22</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="2">
+      <c r="B37" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="3">
         <v>43.33</v>
       </c>
-      <c r="D37" s="2">
+      <c r="E37" s="3">
         <v>3.33</v>
       </c>
-      <c r="E37" s="2">
+      <c r="F37" s="3">
         <v>13.94</v>
       </c>
-      <c r="F37" s="2">
+      <c r="G37" s="3">
         <v>12.9</v>
       </c>
-      <c r="G37" s="2">
+      <c r="H37" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H37" s="2">
+      <c r="I37" s="3">
         <v>7</v>
       </c>
-      <c r="I37" s="2">
+      <c r="J37" s="3">
         <v>11.26</v>
       </c>
-      <c r="J37" s="2">
+      <c r="K37" s="3">
         <v>3.4</v>
       </c>
-      <c r="K37" s="2">
+      <c r="L37" s="3">
         <v>2.21</v>
       </c>
-      <c r="L37" s="2">
+      <c r="M37" s="3">
         <v>0.79</v>
       </c>
-      <c r="M37" s="3">
+      <c r="N37" s="2">
         <v>1.319</v>
       </c>
-      <c r="N37" s="3">
+      <c r="O37" s="2">
         <v>0.25800000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="B38" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="3">
         <v>42.66</v>
       </c>
-      <c r="D38" s="2">
+      <c r="E38" s="3">
         <v>3.54</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="3">
         <v>14.04</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="3">
         <v>12.9</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="3">
         <v>0.15</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="3">
         <v>6.54</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="3">
         <v>11.68</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="3">
         <v>3.55</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="3">
         <v>2.3199999999999998</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="3">
         <v>0.84</v>
       </c>
-      <c r="M38" s="3">
+      <c r="N38" s="2">
         <v>1.345</v>
       </c>
-      <c r="N38" s="3">
+      <c r="O38" s="2">
         <v>0.27900000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="B39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="3">
         <v>42.04</v>
       </c>
-      <c r="D39" s="2">
+      <c r="E39" s="3">
         <v>3.47</v>
       </c>
-      <c r="E39" s="2">
+      <c r="F39" s="3">
         <v>14.26</v>
       </c>
-      <c r="F39" s="2">
+      <c r="G39" s="3">
         <v>12.9</v>
       </c>
-      <c r="G39" s="2">
+      <c r="H39" s="3">
         <v>0.18</v>
       </c>
-      <c r="H39" s="2">
+      <c r="I39" s="3">
         <v>5.84</v>
       </c>
-      <c r="I39" s="2">
+      <c r="J39" s="3">
         <v>11.76</v>
       </c>
-      <c r="J39" s="2">
+      <c r="K39" s="3">
         <v>3.87</v>
       </c>
-      <c r="K39" s="2">
+      <c r="L39" s="3">
         <v>2.41</v>
       </c>
-      <c r="L39" s="2">
+      <c r="M39" s="3">
         <v>0.96</v>
       </c>
-      <c r="M39" s="3">
+      <c r="N39" s="2">
         <v>1.921</v>
       </c>
-      <c r="N39" s="3">
+      <c r="O39" s="2">
         <v>0.371</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="2">
+      <c r="B40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="3">
         <v>42.6</v>
       </c>
-      <c r="D40" s="2">
+      <c r="E40" s="3">
         <v>3.38</v>
       </c>
-      <c r="E40" s="2">
+      <c r="F40" s="3">
         <v>13.82</v>
       </c>
-      <c r="F40" s="2">
+      <c r="G40" s="3">
         <v>12.9</v>
       </c>
-      <c r="G40" s="2">
+      <c r="H40" s="3">
         <v>0.17</v>
       </c>
-      <c r="H40" s="2">
+      <c r="I40" s="3">
         <v>6.86</v>
       </c>
-      <c r="I40" s="2">
+      <c r="J40" s="3">
         <v>11.69</v>
       </c>
-      <c r="J40" s="2">
+      <c r="K40" s="3">
         <v>3.45</v>
       </c>
-      <c r="K40" s="2">
+      <c r="L40" s="3">
         <v>2.2799999999999998</v>
       </c>
-      <c r="L40" s="2">
+      <c r="M40" s="3">
         <v>0.9</v>
       </c>
-      <c r="M40" s="3">
+      <c r="N40" s="2">
         <v>1.585</v>
       </c>
-      <c r="N40" s="3">
+      <c r="O40" s="2">
         <v>0.34100000000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="2">
+      <c r="B41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="3">
         <v>44.1</v>
       </c>
-      <c r="D41" s="2">
+      <c r="E41" s="3">
         <v>3.33</v>
       </c>
-      <c r="E41" s="2">
+      <c r="F41" s="3">
         <v>13.43</v>
       </c>
-      <c r="F41" s="2">
+      <c r="G41" s="3">
         <v>12.9</v>
       </c>
-      <c r="G41" s="2">
+      <c r="H41" s="3">
         <v>0.17</v>
       </c>
-      <c r="H41" s="2">
+      <c r="I41" s="3">
         <v>7.01</v>
       </c>
-      <c r="I41" s="2">
+      <c r="J41" s="3">
         <v>11.44</v>
       </c>
-      <c r="J41" s="2">
+      <c r="K41" s="3">
         <v>3.35</v>
       </c>
-      <c r="K41" s="2">
+      <c r="L41" s="3">
         <v>2.19</v>
       </c>
-      <c r="L41" s="2">
+      <c r="M41" s="3">
         <v>0.79</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="2">
         <v>0.85399999999999998</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="2">
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" s="2">
+      <c r="B42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="3">
         <v>42.27</v>
       </c>
-      <c r="D42" s="2">
+      <c r="E42" s="3">
         <v>3.63</v>
       </c>
-      <c r="E42" s="2">
+      <c r="F42" s="3">
         <v>13.51</v>
       </c>
-      <c r="F42" s="2">
+      <c r="G42" s="3">
         <v>12.9</v>
       </c>
-      <c r="G42" s="2">
+      <c r="H42" s="3">
         <v>0.18</v>
       </c>
-      <c r="H42" s="2">
+      <c r="I42" s="3">
         <v>6.56</v>
       </c>
-      <c r="I42" s="2">
+      <c r="J42" s="3">
         <v>11.86</v>
       </c>
-      <c r="J42" s="2">
+      <c r="K42" s="3">
         <v>3.5</v>
       </c>
-      <c r="K42" s="2">
+      <c r="L42" s="3">
         <v>2.13</v>
       </c>
-      <c r="L42" s="2">
+      <c r="M42" s="3">
         <v>0.86</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="2">
         <v>2.2309999999999999</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="2">
         <v>0.437</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="2">
+      <c r="B43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="3">
         <v>42.59</v>
       </c>
-      <c r="D43" s="2">
+      <c r="E43" s="3">
         <v>3.3</v>
       </c>
-      <c r="E43" s="2">
+      <c r="F43" s="3">
         <v>11.7</v>
       </c>
-      <c r="F43" s="2">
+      <c r="G43" s="3">
         <v>12.9</v>
       </c>
-      <c r="G43" s="2">
+      <c r="H43" s="3">
         <v>0.19</v>
       </c>
-      <c r="H43" s="2">
+      <c r="I43" s="3">
         <v>10.88</v>
       </c>
-      <c r="I43" s="2">
+      <c r="J43" s="3">
         <v>11.25</v>
       </c>
-      <c r="J43" s="2">
+      <c r="K43" s="3">
         <v>2.79</v>
       </c>
-      <c r="K43" s="2">
+      <c r="L43" s="3">
         <v>2.13</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="3">
         <v>0.89</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="2">
         <v>1.0249999999999999</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="2">
         <v>0.20499999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="2">
+      <c r="B44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="3">
         <v>42.69</v>
       </c>
-      <c r="D44" s="2">
+      <c r="E44" s="3">
         <v>3.39</v>
       </c>
-      <c r="E44" s="2">
+      <c r="F44" s="3">
         <v>14.1</v>
       </c>
-      <c r="F44" s="2">
+      <c r="G44" s="3">
         <v>12.9</v>
       </c>
-      <c r="G44" s="2">
+      <c r="H44" s="3">
         <v>0.16</v>
       </c>
-      <c r="H44" s="2">
+      <c r="I44" s="3">
         <v>6.6</v>
       </c>
-      <c r="I44" s="2">
+      <c r="J44" s="3">
         <v>11.46</v>
       </c>
-      <c r="J44" s="2">
+      <c r="K44" s="3">
         <v>3.43</v>
       </c>
-      <c r="K44" s="2">
+      <c r="L44" s="3">
         <v>2.15</v>
       </c>
-      <c r="L44" s="2">
+      <c r="M44" s="3">
         <v>0.86</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="2">
         <v>1.887</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="2">
         <v>0.34</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="2">
+      <c r="B45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="3">
         <v>44.9</v>
       </c>
-      <c r="D45" s="2">
+      <c r="E45" s="3">
         <v>3.06</v>
       </c>
-      <c r="E45" s="2">
+      <c r="F45" s="3">
         <v>11.06</v>
       </c>
-      <c r="F45" s="2">
+      <c r="G45" s="3">
         <v>12</v>
       </c>
-      <c r="G45" s="2">
+      <c r="H45" s="3">
         <v>0.13</v>
       </c>
-      <c r="H45" s="2">
+      <c r="I45" s="3">
         <v>9.98</v>
       </c>
-      <c r="I45" s="2">
+      <c r="J45" s="3">
         <v>12.22</v>
       </c>
-      <c r="J45" s="2">
+      <c r="K45" s="3">
         <v>3.39</v>
       </c>
-      <c r="K45" s="2">
+      <c r="L45" s="3">
         <v>1.57</v>
       </c>
-      <c r="L45" s="2">
+      <c r="M45" s="3">
         <v>0.69</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="2">
         <v>0.59499999999999997</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="2">
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="2">
+      <c r="B46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" s="3">
         <v>44.4</v>
       </c>
-      <c r="D46" s="2">
+      <c r="E46" s="3">
         <v>3.15</v>
       </c>
-      <c r="E46" s="2">
+      <c r="F46" s="3">
         <v>10.96</v>
       </c>
-      <c r="F46" s="2">
+      <c r="G46" s="3">
         <v>12</v>
       </c>
-      <c r="G46" s="2">
+      <c r="H46" s="3">
         <v>0.13</v>
       </c>
-      <c r="H46" s="2">
+      <c r="I46" s="3">
         <v>10.78</v>
       </c>
-      <c r="I46" s="2">
+      <c r="J46" s="3">
         <v>11.69</v>
       </c>
-      <c r="J46" s="2">
+      <c r="K46" s="3">
         <v>3.31</v>
       </c>
-      <c r="K46" s="2">
+      <c r="L46" s="3">
         <v>1.75</v>
       </c>
-      <c r="L46" s="2">
+      <c r="M46" s="3">
         <v>0.54</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="2">
         <v>0.89300000000000002</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="2">
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="2">
+      <c r="B47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="3">
         <v>42.8</v>
       </c>
-      <c r="D47" s="2">
+      <c r="E47" s="3">
         <v>2.57</v>
       </c>
-      <c r="E47" s="2">
+      <c r="F47" s="3">
         <v>10.86</v>
       </c>
-      <c r="F47" s="2">
+      <c r="G47" s="3">
         <v>12</v>
       </c>
-      <c r="G47" s="2">
+      <c r="H47" s="3">
         <v>0.15</v>
       </c>
-      <c r="H47" s="2">
+      <c r="I47" s="3">
         <v>10.15</v>
       </c>
-      <c r="I47" s="2">
+      <c r="J47" s="3">
         <v>12.5</v>
       </c>
-      <c r="J47" s="2">
+      <c r="K47" s="3">
         <v>3.07</v>
       </c>
-      <c r="K47" s="2">
+      <c r="L47" s="3">
         <v>2.09</v>
       </c>
-      <c r="L47" s="2">
+      <c r="M47" s="3">
         <v>0.77</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="2">
         <v>2.669</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="2">
         <v>0.98</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="2">
+      <c r="B48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="3">
         <v>42.18</v>
       </c>
-      <c r="D48" s="2">
+      <c r="E48" s="3">
         <v>3.04</v>
       </c>
-      <c r="E48" s="2">
+      <c r="F48" s="3">
         <v>10.93</v>
       </c>
-      <c r="F48" s="2">
+      <c r="G48" s="3">
         <v>12</v>
       </c>
-      <c r="G48" s="2">
+      <c r="H48" s="3">
         <v>0.13</v>
       </c>
-      <c r="H48" s="2">
+      <c r="I48" s="3">
         <v>11</v>
       </c>
-      <c r="I48" s="2">
+      <c r="J48" s="3">
         <v>13.19</v>
       </c>
-      <c r="J48" s="2">
+      <c r="K48" s="3">
         <v>3.18</v>
       </c>
-      <c r="K48" s="2">
+      <c r="L48" s="3">
         <v>1.68</v>
       </c>
-      <c r="L48" s="2">
+      <c r="M48" s="3">
         <v>0.64</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="2">
         <v>1.653</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="2">
         <v>0.58199999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="B49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="3">
         <v>43.15</v>
       </c>
-      <c r="D49" s="2">
+      <c r="E49" s="3">
         <v>3.26</v>
       </c>
-      <c r="E49" s="2">
+      <c r="F49" s="3">
         <v>10.65</v>
       </c>
-      <c r="F49" s="2">
+      <c r="G49" s="3">
         <v>12</v>
       </c>
-      <c r="G49" s="2">
+      <c r="H49" s="3">
         <v>0.11</v>
       </c>
-      <c r="H49" s="2">
+      <c r="I49" s="3">
         <v>9.18</v>
       </c>
-      <c r="I49" s="2">
+      <c r="J49" s="3">
         <v>13.89</v>
       </c>
-      <c r="J49" s="2">
+      <c r="K49" s="3">
         <v>3.3</v>
       </c>
-      <c r="K49" s="2">
+      <c r="L49" s="3">
         <v>1.49</v>
       </c>
-      <c r="L49" s="2">
+      <c r="M49" s="3">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="2">
         <v>1.9830000000000001</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="2">
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C50" s="2">
+      <c r="B50" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="3">
         <v>42.49</v>
       </c>
-      <c r="D50" s="2">
+      <c r="E50" s="3">
         <v>3.22</v>
       </c>
-      <c r="E50" s="2">
+      <c r="F50" s="3">
         <v>11.38</v>
       </c>
-      <c r="F50" s="2">
+      <c r="G50" s="3">
         <v>12</v>
       </c>
-      <c r="G50" s="2">
+      <c r="H50" s="3">
         <v>0.13</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="3">
         <v>8.83</v>
       </c>
-      <c r="I50" s="2">
+      <c r="J50" s="3">
         <v>14.38</v>
       </c>
-      <c r="J50" s="2">
+      <c r="K50" s="3">
         <v>3.13</v>
       </c>
-      <c r="K50" s="2">
+      <c r="L50" s="3">
         <v>1.44</v>
       </c>
-      <c r="L50" s="2">
+      <c r="M50" s="3">
         <v>1.39</v>
       </c>
-      <c r="M50" s="3">
+      <c r="N50" s="2">
         <v>1.194</v>
       </c>
-      <c r="N50" s="3">
+      <c r="O50" s="2">
         <v>0.185</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C51" s="2">
+      <c r="B51" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" s="3">
         <v>44.42</v>
       </c>
-      <c r="D51" s="2">
+      <c r="E51" s="3">
         <v>3.47</v>
       </c>
-      <c r="E51" s="2">
+      <c r="F51" s="3">
         <v>11.22</v>
       </c>
-      <c r="F51" s="2">
+      <c r="G51" s="3">
         <v>12</v>
       </c>
-      <c r="G51" s="2">
+      <c r="H51" s="3">
         <v>0.09</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="3">
         <v>10.36</v>
       </c>
-      <c r="I51" s="2">
+      <c r="J51" s="3">
         <v>11.25</v>
       </c>
-      <c r="J51" s="2">
+      <c r="K51" s="3">
         <v>3.4</v>
       </c>
-      <c r="K51" s="2">
+      <c r="L51" s="3">
         <v>1.51</v>
       </c>
-      <c r="L51" s="2">
+      <c r="M51" s="3">
         <v>0.32</v>
       </c>
-      <c r="M51" s="3">
+      <c r="N51" s="2">
         <v>1.595</v>
       </c>
-      <c r="N51" s="3">
+      <c r="O51" s="2">
         <v>0.70899999999999996</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C52" s="2">
+      <c r="B52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" s="3">
         <v>42.91</v>
       </c>
-      <c r="D52" s="2">
+      <c r="E52" s="3">
         <v>4.1399999999999997</v>
       </c>
-      <c r="E52" s="2">
+      <c r="F52" s="3">
         <v>10.91</v>
       </c>
-      <c r="F52" s="2">
+      <c r="G52" s="3">
         <v>12</v>
       </c>
-      <c r="G52" s="2">
+      <c r="H52" s="3">
         <v>0.18</v>
       </c>
-      <c r="H52" s="2">
+      <c r="I52" s="3">
         <v>9.1300000000000008</v>
       </c>
-      <c r="I52" s="2">
+      <c r="J52" s="3">
         <v>13.82</v>
       </c>
-      <c r="J52" s="2">
+      <c r="K52" s="3">
         <v>3.18</v>
       </c>
-      <c r="K52" s="2">
+      <c r="L52" s="3">
         <v>1.62</v>
       </c>
-      <c r="L52" s="2">
+      <c r="M52" s="3">
         <v>0.75</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="2">
         <v>0.96</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="2">
         <v>0.38200000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="2">
+      <c r="B53" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" s="3">
         <v>43.76</v>
       </c>
-      <c r="D53" s="2">
+      <c r="E53" s="3">
         <v>3.26</v>
       </c>
-      <c r="E53" s="2">
+      <c r="F53" s="3">
         <v>11.59</v>
       </c>
-      <c r="F53" s="2">
+      <c r="G53" s="3">
         <v>12</v>
       </c>
-      <c r="G53" s="2">
+      <c r="H53" s="3">
         <v>0.12</v>
       </c>
-      <c r="H53" s="2">
+      <c r="I53" s="3">
         <v>10.27</v>
       </c>
-      <c r="I53" s="2">
+      <c r="J53" s="3">
         <v>12.47</v>
       </c>
-      <c r="J53" s="2">
+      <c r="K53" s="3">
         <v>2.97</v>
       </c>
-      <c r="K53" s="2">
+      <c r="L53" s="3">
         <v>1.64</v>
       </c>
-      <c r="L53" s="2">
+      <c r="M53" s="3">
         <v>0.86</v>
       </c>
-      <c r="M53" s="3">
+      <c r="N53" s="2">
         <v>0.65600000000000003</v>
       </c>
-      <c r="N53" s="3">
+      <c r="O53" s="2">
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="2">
+      <c r="B54" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="3">
         <v>42.64</v>
       </c>
-      <c r="D54" s="2">
+      <c r="E54" s="3">
         <v>2.8</v>
       </c>
-      <c r="E54" s="2">
+      <c r="F54" s="3">
         <v>10.75</v>
       </c>
-      <c r="F54" s="2">
+      <c r="G54" s="3">
         <v>12</v>
       </c>
-      <c r="G54" s="2">
+      <c r="H54" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H54" s="2">
+      <c r="I54" s="3">
         <v>10.17</v>
       </c>
-      <c r="I54" s="2">
+      <c r="J54" s="3">
         <v>13.46</v>
       </c>
-      <c r="J54" s="2">
+      <c r="K54" s="3">
         <v>3.24</v>
       </c>
-      <c r="K54" s="2">
+      <c r="L54" s="3">
         <v>1.44</v>
       </c>
-      <c r="L54" s="2">
+      <c r="M54" s="3">
         <v>0.86</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="2">
         <v>2.117</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="2">
         <v>0.879</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" s="2">
+      <c r="B55" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" s="3">
         <v>41.02</v>
       </c>
-      <c r="D55" s="2">
+      <c r="E55" s="3">
         <v>4.01</v>
       </c>
-      <c r="E55" s="2">
+      <c r="F55" s="3">
         <v>12.2</v>
       </c>
-      <c r="F55" s="2">
+      <c r="G55" s="3">
         <v>12</v>
       </c>
-      <c r="G55" s="2">
+      <c r="H55" s="3">
         <v>0.17</v>
       </c>
-      <c r="H55" s="2">
+      <c r="I55" s="3">
         <v>9.81</v>
       </c>
-      <c r="I55" s="2">
+      <c r="J55" s="3">
         <v>11.95</v>
       </c>
-      <c r="J55" s="2">
+      <c r="K55" s="3">
         <v>3.63</v>
       </c>
-      <c r="K55" s="2">
+      <c r="L55" s="3">
         <v>1.86</v>
       </c>
-      <c r="L55" s="2">
+      <c r="M55" s="3">
         <v>0.84</v>
       </c>
-      <c r="M55" s="3">
+      <c r="N55" s="2">
         <v>2.145</v>
       </c>
-      <c r="N55" s="3">
+      <c r="O55" s="2">
         <v>0.69299999999999995</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="2">
+      <c r="B56" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" s="3">
         <v>44.37</v>
       </c>
-      <c r="D56" s="2">
+      <c r="E56" s="3">
         <v>3.41</v>
       </c>
-      <c r="E56" s="2">
+      <c r="F56" s="3">
         <v>11.1</v>
       </c>
-      <c r="F56" s="2">
+      <c r="G56" s="3">
         <v>12</v>
       </c>
-      <c r="G56" s="2">
+      <c r="H56" s="3">
         <v>0.15</v>
       </c>
-      <c r="H56" s="2">
+      <c r="I56" s="3">
         <v>8.86</v>
       </c>
-      <c r="I56" s="2">
+      <c r="J56" s="3">
         <v>12.8</v>
       </c>
-      <c r="J56" s="2">
+      <c r="K56" s="3">
         <v>3.45</v>
       </c>
-      <c r="K56" s="2">
+      <c r="L56" s="3">
         <v>1.75</v>
       </c>
-      <c r="L56" s="2">
+      <c r="M56" s="3">
         <v>0.74</v>
       </c>
-      <c r="M56" s="3">
+      <c r="N56" s="2">
         <v>0.98099999999999998</v>
       </c>
-      <c r="N56" s="3">
+      <c r="O56" s="2">
         <v>0.124</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C57" s="2">
+      <c r="B57" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D57" s="3">
         <v>44.3</v>
       </c>
-      <c r="D57" s="2">
+      <c r="E57" s="3">
         <v>3.52</v>
       </c>
-      <c r="E57" s="2">
+      <c r="F57" s="3">
         <v>10.91</v>
       </c>
-      <c r="F57" s="2">
+      <c r="G57" s="3">
         <v>12</v>
       </c>
-      <c r="G57" s="2">
+      <c r="H57" s="3">
         <v>0.15</v>
       </c>
-      <c r="H57" s="2">
+      <c r="I57" s="3">
         <v>8.7899999999999991</v>
       </c>
-      <c r="I57" s="2">
+      <c r="J57" s="3">
         <v>12.89</v>
       </c>
-      <c r="J57" s="2">
+      <c r="K57" s="3">
         <v>3.3</v>
       </c>
-      <c r="K57" s="2">
+      <c r="L57" s="3">
         <v>1.68</v>
       </c>
-      <c r="L57" s="2">
+      <c r="M57" s="3">
         <v>0.75</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="2">
         <v>1.3120000000000001</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="2">
         <v>0.182</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="2">
+      <c r="B58" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D58" s="3">
         <v>43.98</v>
       </c>
-      <c r="D58" s="2">
+      <c r="E58" s="3">
         <v>3.81</v>
       </c>
-      <c r="E58" s="2">
+      <c r="F58" s="3">
         <v>11.06</v>
       </c>
-      <c r="F58" s="2">
+      <c r="G58" s="3">
         <v>12</v>
       </c>
-      <c r="G58" s="2">
+      <c r="H58" s="3">
         <v>0.15</v>
       </c>
-      <c r="H58" s="2">
+      <c r="I58" s="3">
         <v>9.4700000000000006</v>
       </c>
-      <c r="I58" s="2">
+      <c r="J58" s="3">
         <v>12.92</v>
       </c>
-      <c r="J58" s="2">
+      <c r="K58" s="3">
         <v>3.14</v>
       </c>
-      <c r="K58" s="2">
+      <c r="L58" s="3">
         <v>1.54</v>
       </c>
-      <c r="L58" s="2">
+      <c r="M58" s="3">
         <v>0.7</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="2">
         <v>0.80900000000000005</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="2">
         <v>0.1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="2">
+      <c r="B59" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="3">
         <v>42.74</v>
       </c>
-      <c r="D59" s="2">
+      <c r="E59" s="3">
         <v>3.11</v>
       </c>
-      <c r="E59" s="2">
+      <c r="F59" s="3">
         <v>11.21</v>
       </c>
-      <c r="F59" s="2">
+      <c r="G59" s="3">
         <v>12</v>
       </c>
-      <c r="G59" s="2">
+      <c r="H59" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H59" s="2">
+      <c r="I59" s="3">
         <v>9.2100000000000009</v>
       </c>
-      <c r="I59" s="2">
+      <c r="J59" s="3">
         <v>13.62</v>
       </c>
-      <c r="J59" s="2">
+      <c r="K59" s="3">
         <v>3.19</v>
       </c>
-      <c r="K59" s="2">
+      <c r="L59" s="3">
         <v>1.53</v>
       </c>
-      <c r="L59" s="2">
+      <c r="M59" s="3">
         <v>0.73</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="2">
         <v>2.133</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="2">
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" s="2">
+      <c r="B60" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="3">
         <v>42.46</v>
       </c>
-      <c r="D60" s="2">
+      <c r="E60" s="3">
         <v>3.1</v>
       </c>
-      <c r="E60" s="2">
+      <c r="F60" s="3">
         <v>11.06</v>
       </c>
-      <c r="F60" s="2">
+      <c r="G60" s="3">
         <v>12</v>
       </c>
-      <c r="G60" s="2">
+      <c r="H60" s="3">
         <v>0.15</v>
       </c>
-      <c r="H60" s="2">
+      <c r="I60" s="3">
         <v>9.3800000000000008</v>
       </c>
-      <c r="I60" s="2">
+      <c r="J60" s="3">
         <v>13.64</v>
       </c>
-      <c r="J60" s="2">
+      <c r="K60" s="3">
         <v>3.42</v>
       </c>
-      <c r="K60" s="2">
+      <c r="L60" s="3">
         <v>1.53</v>
       </c>
-      <c r="L60" s="2">
+      <c r="M60" s="3">
         <v>0.73</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="2">
         <v>2.149</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="2">
         <v>0.80400000000000005</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="2">
+      <c r="B61" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61" s="3">
         <v>44.37</v>
       </c>
-      <c r="D61" s="2">
+      <c r="E61" s="3">
         <v>3.04</v>
       </c>
-      <c r="E61" s="2">
+      <c r="F61" s="3">
         <v>10.37</v>
       </c>
-      <c r="F61" s="2">
+      <c r="G61" s="3">
         <v>12</v>
       </c>
-      <c r="G61" s="2">
+      <c r="H61" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H61" s="2">
+      <c r="I61" s="3">
         <v>9.7200000000000006</v>
       </c>
-      <c r="I61" s="2">
+      <c r="J61" s="3">
         <v>13.82</v>
       </c>
-      <c r="J61" s="2">
+      <c r="K61" s="3">
         <v>3.06</v>
       </c>
-      <c r="K61" s="2">
+      <c r="L61" s="3">
         <v>1.37</v>
       </c>
-      <c r="L61" s="2">
+      <c r="M61" s="3">
         <v>0.49</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="2">
         <v>1.2170000000000001</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="2">
         <v>0.50900000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C62" s="2">
+      <c r="B62" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D62" s="3">
         <v>42.15</v>
       </c>
-      <c r="D62" s="2">
+      <c r="E62" s="3">
         <v>3.37</v>
       </c>
-      <c r="E62" s="2">
+      <c r="F62" s="3">
         <v>12.33</v>
       </c>
-      <c r="F62" s="2">
+      <c r="G62" s="3">
         <v>12</v>
       </c>
-      <c r="G62" s="2">
+      <c r="H62" s="3">
         <v>0.18</v>
       </c>
-      <c r="H62" s="2">
+      <c r="I62" s="3">
         <v>10</v>
       </c>
-      <c r="I62" s="2">
+      <c r="J62" s="3">
         <v>11.92</v>
       </c>
-      <c r="J62" s="2">
+      <c r="K62" s="3">
         <v>4.66</v>
       </c>
-      <c r="K62" s="2">
+      <c r="L62" s="3">
         <v>1.95</v>
       </c>
-      <c r="L62" s="2">
+      <c r="M62" s="3">
         <v>0.7</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="2">
         <v>0.3</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="2">
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C63" s="2">
+      <c r="B63" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" s="3">
         <v>44.55</v>
       </c>
-      <c r="D63" s="2">
+      <c r="E63" s="3">
         <v>3.29</v>
       </c>
-      <c r="E63" s="2">
+      <c r="F63" s="3">
         <v>11.04</v>
       </c>
-      <c r="F63" s="2">
+      <c r="G63" s="3">
         <v>12</v>
       </c>
-      <c r="G63" s="2">
+      <c r="H63" s="3">
         <v>0.12</v>
       </c>
-      <c r="H63" s="2">
+      <c r="I63" s="3">
         <v>9.2100000000000009</v>
       </c>
-      <c r="I63" s="2">
+      <c r="J63" s="3">
         <v>12.9</v>
       </c>
-      <c r="J63" s="2">
+      <c r="K63" s="3">
         <v>3.43</v>
       </c>
-      <c r="K63" s="2">
+      <c r="L63" s="3">
         <v>1.8</v>
       </c>
-      <c r="L63" s="2">
+      <c r="M63" s="3">
         <v>0.47</v>
       </c>
-      <c r="M63" s="3">
+      <c r="N63" s="2">
         <v>0.78100000000000003</v>
       </c>
-      <c r="N63" s="3">
+      <c r="O63" s="2">
         <v>0.126</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" s="2">
+      <c r="B64" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" s="3">
         <v>45.52</v>
       </c>
-      <c r="D64" s="2">
+      <c r="E64" s="3">
         <v>2.87</v>
       </c>
-      <c r="E64" s="2">
+      <c r="F64" s="3">
         <v>10.83</v>
       </c>
-      <c r="F64" s="2">
+      <c r="G64" s="3">
         <v>12</v>
       </c>
-      <c r="G64" s="2">
+      <c r="H64" s="3">
         <v>0.11</v>
       </c>
-      <c r="H64" s="2">
+      <c r="I64" s="3">
         <v>10.029999999999999</v>
       </c>
-      <c r="I64" s="2">
+      <c r="J64" s="3">
         <v>11.4</v>
       </c>
-      <c r="J64" s="2">
+      <c r="K64" s="3">
         <v>3.45</v>
       </c>
-      <c r="K64" s="2">
+      <c r="L64" s="3">
         <v>1.53</v>
       </c>
-      <c r="L64" s="2">
+      <c r="M64" s="3">
         <v>0.61</v>
       </c>
-      <c r="M64" s="3">
+      <c r="N64" s="2">
         <v>1.2849999999999999</v>
       </c>
-      <c r="N64" s="3">
+      <c r="O64" s="2">
         <v>0.51500000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65" s="2">
+      <c r="B65" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" s="3">
         <v>42.68</v>
       </c>
-      <c r="D65" s="2">
+      <c r="E65" s="3">
         <v>3.53</v>
       </c>
-      <c r="E65" s="2">
+      <c r="F65" s="3">
         <v>11.77</v>
       </c>
-      <c r="F65" s="2">
+      <c r="G65" s="3">
         <v>12</v>
       </c>
-      <c r="G65" s="2">
+      <c r="H65" s="3">
         <v>0.16</v>
       </c>
-      <c r="H65" s="2">
+      <c r="I65" s="3">
         <v>7.57</v>
       </c>
-      <c r="I65" s="2">
+      <c r="J65" s="3">
         <v>14.35</v>
       </c>
-      <c r="J65" s="2">
+      <c r="K65" s="3">
         <v>3.95</v>
       </c>
-      <c r="K65" s="2">
+      <c r="L65" s="3">
         <v>1.66</v>
       </c>
-      <c r="L65" s="2">
+      <c r="M65" s="3">
         <v>0.76</v>
       </c>
-      <c r="M65" s="3">
+      <c r="N65" s="2">
         <v>1.083</v>
       </c>
-      <c r="N65" s="3">
+      <c r="O65" s="2">
         <v>0.44400000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" s="2">
+      <c r="B66" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="3">
         <v>44.47</v>
       </c>
-      <c r="D66" s="2">
+      <c r="E66" s="3">
         <v>2.71</v>
       </c>
-      <c r="E66" s="2">
+      <c r="F66" s="3">
         <v>11.38</v>
       </c>
-      <c r="F66" s="2">
+      <c r="G66" s="3">
         <v>12</v>
       </c>
-      <c r="G66" s="2">
+      <c r="H66" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H66" s="2">
+      <c r="I66" s="3">
         <v>7.84</v>
       </c>
-      <c r="I66" s="2">
+      <c r="J66" s="3">
         <v>13.79</v>
       </c>
-      <c r="J66" s="2">
+      <c r="K66" s="3">
         <v>3.37</v>
       </c>
-      <c r="K66" s="2">
+      <c r="L66" s="3">
         <v>1.5</v>
       </c>
-      <c r="L66" s="2">
+      <c r="M66" s="3">
         <v>0.6</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="2">
         <v>1.7929999999999999</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="2">
         <v>0.72099999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C67" s="2">
+      <c r="B67" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" s="3">
         <v>45.67</v>
       </c>
-      <c r="D67" s="2">
+      <c r="E67" s="3">
         <v>2.8</v>
       </c>
-      <c r="E67" s="2">
+      <c r="F67" s="3">
         <v>11.7</v>
       </c>
-      <c r="F67" s="2">
+      <c r="G67" s="3">
         <v>12</v>
       </c>
-      <c r="G67" s="2">
+      <c r="H67" s="3">
         <v>0.08</v>
       </c>
-      <c r="H67" s="2">
+      <c r="I67" s="3">
         <v>10.16</v>
       </c>
-      <c r="I67" s="2">
+      <c r="J67" s="3">
         <v>9.9499999999999993</v>
       </c>
-      <c r="J67" s="2">
+      <c r="K67" s="3">
         <v>3.91</v>
       </c>
-      <c r="K67" s="2">
+      <c r="L67" s="3">
         <v>1.66</v>
       </c>
-      <c r="L67" s="2">
+      <c r="M67" s="3">
         <v>0.63</v>
       </c>
-      <c r="M67" s="3">
+      <c r="N67" s="2">
         <v>1.069</v>
       </c>
-      <c r="N67" s="3">
+      <c r="O67" s="2">
         <v>0.36499999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C68" s="2">
+      <c r="B68" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="3">
         <v>44.83</v>
       </c>
-      <c r="D68" s="2">
+      <c r="E68" s="3">
         <v>2.97</v>
       </c>
-      <c r="E68" s="2">
+      <c r="F68" s="3">
         <v>11.06</v>
       </c>
-      <c r="F68" s="2">
+      <c r="G68" s="3">
         <v>12</v>
       </c>
-      <c r="G68" s="2">
+      <c r="H68" s="3">
         <v>0.08</v>
       </c>
-      <c r="H68" s="2">
+      <c r="I68" s="3">
         <v>9.84</v>
       </c>
-      <c r="I68" s="2">
+      <c r="J68" s="3">
         <v>12.4</v>
       </c>
-      <c r="J68" s="2">
+      <c r="K68" s="3">
         <v>3.4</v>
       </c>
-      <c r="K68" s="2">
+      <c r="L68" s="3">
         <v>1.4</v>
       </c>
-      <c r="L68" s="2">
+      <c r="M68" s="3">
         <v>0.45</v>
       </c>
-      <c r="M68" s="3">
+      <c r="N68" s="2">
         <v>1.1739999999999999</v>
       </c>
-      <c r="N68" s="3">
+      <c r="O68" s="2">
         <v>0.14099999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C69" s="2">
+      <c r="B69" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D69" s="3">
         <v>45.68</v>
       </c>
-      <c r="D69" s="2">
+      <c r="E69" s="3">
         <v>2.86</v>
       </c>
-      <c r="E69" s="2">
+      <c r="F69" s="3">
         <v>10.97</v>
       </c>
-      <c r="F69" s="2">
+      <c r="G69" s="3">
         <v>12</v>
       </c>
-      <c r="G69" s="2">
+      <c r="H69" s="3">
         <v>0.12</v>
       </c>
-      <c r="H69" s="2">
+      <c r="I69" s="3">
         <v>9.1</v>
       </c>
-      <c r="I69" s="2">
+      <c r="J69" s="3">
         <v>11.81</v>
       </c>
-      <c r="J69" s="2">
+      <c r="K69" s="3">
         <v>4.2300000000000004</v>
       </c>
-      <c r="K69" s="2">
+      <c r="L69" s="3">
         <v>1.56</v>
       </c>
-      <c r="L69" s="2">
+      <c r="M69" s="3">
         <v>0.8</v>
       </c>
-      <c r="M69" s="3">
+      <c r="N69" s="2">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N69" s="3">
+      <c r="O69" s="2">
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C70" s="2">
+      <c r="B70" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D70" s="3">
         <v>44.85</v>
       </c>
-      <c r="D70" s="2">
+      <c r="E70" s="3">
         <v>3.2</v>
       </c>
-      <c r="E70" s="2">
+      <c r="F70" s="3">
         <v>12.38</v>
       </c>
-      <c r="F70" s="2">
+      <c r="G70" s="3">
         <v>12</v>
       </c>
-      <c r="G70" s="2">
+      <c r="H70" s="3">
         <v>0.06</v>
       </c>
-      <c r="H70" s="2">
+      <c r="I70" s="3">
         <v>9.66</v>
       </c>
-      <c r="I70" s="2">
+      <c r="J70" s="3">
         <v>11.23</v>
       </c>
-      <c r="J70" s="2">
+      <c r="K70" s="3">
         <v>3.35</v>
       </c>
-      <c r="K70" s="2">
+      <c r="L70" s="3">
         <v>1.51</v>
       </c>
-      <c r="L70" s="2">
+      <c r="M70" s="3">
         <v>0.38</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="2">
         <v>1.0009999999999999</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="2">
         <v>0.502</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71" s="2">
+      <c r="B71" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71" s="3">
         <v>42.7</v>
       </c>
-      <c r="D71" s="2">
+      <c r="E71" s="3">
         <v>4.97</v>
       </c>
-      <c r="E71" s="2">
+      <c r="F71" s="3">
         <v>12.14</v>
       </c>
-      <c r="F71" s="2">
+      <c r="G71" s="3">
         <v>12</v>
       </c>
-      <c r="G71" s="2">
+      <c r="H71" s="3">
         <v>0.12</v>
       </c>
-      <c r="H71" s="2">
+      <c r="I71" s="3">
         <v>10.93</v>
       </c>
-      <c r="I71" s="2">
+      <c r="J71" s="3">
         <v>10.46</v>
       </c>
-      <c r="J71" s="2">
+      <c r="K71" s="3">
         <v>2.65</v>
       </c>
-      <c r="K71" s="2">
+      <c r="L71" s="3">
         <v>2.1</v>
       </c>
-      <c r="L71" s="2">
+      <c r="M71" s="3">
         <v>0.3</v>
       </c>
-      <c r="M71" s="3">
+      <c r="N71" s="2">
         <v>1.2969999999999999</v>
       </c>
-      <c r="N71" s="3">
+      <c r="O71" s="2">
         <v>0.46899999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72" s="2" t="s">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C72" s="2">
+      <c r="B72" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D72" s="3">
         <v>43.3</v>
       </c>
-      <c r="D72" s="2">
+      <c r="E72" s="3">
         <v>4.01</v>
       </c>
-      <c r="E72" s="2">
+      <c r="F72" s="3">
         <v>13.12</v>
       </c>
-      <c r="F72" s="2">
+      <c r="G72" s="3">
         <v>12</v>
       </c>
-      <c r="G72" s="2">
+      <c r="H72" s="3">
         <v>0.11</v>
       </c>
-      <c r="H72" s="2">
+      <c r="I72" s="3">
         <v>7.39</v>
       </c>
-      <c r="I72" s="2">
+      <c r="J72" s="3">
         <v>12.76</v>
       </c>
-      <c r="J72" s="2">
+      <c r="K72" s="3">
         <v>2.77</v>
       </c>
-      <c r="K72" s="2">
+      <c r="L72" s="3">
         <v>1.77</v>
       </c>
-      <c r="L72" s="2">
+      <c r="M72" s="3">
         <v>0.68</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="2">
         <v>1.7210000000000001</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="2">
         <v>0.63500000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C73" s="2">
+      <c r="B73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D73" s="3">
         <v>43.34</v>
       </c>
-      <c r="D73" s="2">
+      <c r="E73" s="3">
         <v>3.51</v>
       </c>
-      <c r="E73" s="2">
+      <c r="F73" s="3">
         <v>11.31</v>
       </c>
-      <c r="F73" s="2">
+      <c r="G73" s="3">
         <v>12</v>
       </c>
-      <c r="G73" s="2">
+      <c r="H73" s="3">
         <v>0.1</v>
       </c>
-      <c r="H73" s="2">
+      <c r="I73" s="3">
         <v>10.65</v>
       </c>
-      <c r="I73" s="2">
+      <c r="J73" s="3">
         <v>11.9</v>
       </c>
-      <c r="J73" s="2">
+      <c r="K73" s="3">
         <v>2.96</v>
       </c>
-      <c r="K73" s="2">
+      <c r="L73" s="3">
         <v>1.72</v>
       </c>
-      <c r="L73" s="2">
+      <c r="M73" s="3">
         <v>0.54</v>
       </c>
-      <c r="M73" s="3">
+      <c r="N73" s="2">
         <v>1.6020000000000001</v>
       </c>
-      <c r="N73" s="3">
+      <c r="O73" s="2">
         <v>1.3109999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C74" s="2">
+      <c r="B74" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="3">
         <v>42.14</v>
       </c>
-      <c r="D74" s="2">
+      <c r="E74" s="3">
         <v>3.55</v>
       </c>
-      <c r="E74" s="2">
+      <c r="F74" s="3">
         <v>13.21</v>
       </c>
-      <c r="F74" s="2">
+      <c r="G74" s="3">
         <v>12</v>
       </c>
-      <c r="G74" s="2">
+      <c r="H74" s="3">
         <v>0.16</v>
       </c>
-      <c r="H74" s="2">
+      <c r="I74" s="3">
         <v>8.33</v>
       </c>
-      <c r="I74" s="2">
+      <c r="J74" s="3">
         <v>13.17</v>
       </c>
-      <c r="J74" s="2">
+      <c r="K74" s="3">
         <v>3.64</v>
       </c>
-      <c r="K74" s="2">
+      <c r="L74" s="3">
         <v>1.8</v>
       </c>
-      <c r="L74" s="2">
+      <c r="M74" s="3">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M74" s="3">
+      <c r="N74" s="2">
         <v>1.02</v>
       </c>
-      <c r="N74" s="3">
+      <c r="O74" s="2">
         <v>1.19</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75" s="2">
+      <c r="B75" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="3">
         <v>40.19</v>
       </c>
-      <c r="D75" s="2">
+      <c r="E75" s="3">
         <v>4.18</v>
       </c>
-      <c r="E75" s="2">
+      <c r="F75" s="3">
         <v>13.2</v>
       </c>
-      <c r="F75" s="2">
+      <c r="G75" s="3">
         <v>12</v>
       </c>
-      <c r="G75" s="2">
+      <c r="H75" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H75" s="2">
+      <c r="I75" s="3">
         <v>10.33</v>
       </c>
-      <c r="I75" s="2">
+      <c r="J75" s="3">
         <v>12.69</v>
       </c>
-      <c r="J75" s="2">
+      <c r="K75" s="3">
         <v>3.53</v>
       </c>
-      <c r="K75" s="2">
+      <c r="L75" s="3">
         <v>1.77</v>
       </c>
-      <c r="L75" s="2">
+      <c r="M75" s="3">
         <v>0.66</v>
       </c>
-      <c r="M75" s="3">
+      <c r="N75" s="2">
         <v>0.93100000000000005</v>
       </c>
-      <c r="N75" s="3">
+      <c r="O75" s="2">
         <v>0.61799999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A76" s="2" t="s">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C76" s="2">
+      <c r="B76" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D76" s="3">
         <v>43.63</v>
       </c>
-      <c r="D76" s="2">
+      <c r="E76" s="3">
         <v>3.68</v>
       </c>
-      <c r="E76" s="2">
+      <c r="F76" s="3">
         <v>12.5</v>
       </c>
-      <c r="F76" s="2">
+      <c r="G76" s="3">
         <v>12</v>
       </c>
-      <c r="G76" s="2">
+      <c r="H76" s="3">
         <v>0.08</v>
       </c>
-      <c r="H76" s="2">
+      <c r="I76" s="3">
         <v>10.72</v>
       </c>
-      <c r="I76" s="2">
+      <c r="J76" s="3">
         <v>10.57</v>
       </c>
-      <c r="J76" s="2">
+      <c r="K76" s="3">
         <v>3.04</v>
       </c>
-      <c r="K76" s="2">
+      <c r="L76" s="3">
         <v>1.66</v>
       </c>
-      <c r="L76" s="2">
+      <c r="M76" s="3">
         <v>0.67</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="2">
         <v>1.083</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="2">
         <v>0.38</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C77" s="2">
+      <c r="B77" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" s="3">
         <v>41.8</v>
       </c>
-      <c r="D77" s="2">
+      <c r="E77" s="3">
         <v>3.76</v>
       </c>
-      <c r="E77" s="2">
+      <c r="F77" s="3">
         <v>12.63</v>
       </c>
-      <c r="F77" s="2">
+      <c r="G77" s="3">
         <v>12</v>
       </c>
-      <c r="G77" s="2">
+      <c r="H77" s="3">
         <v>0.1</v>
       </c>
-      <c r="H77" s="2">
+      <c r="I77" s="3">
         <v>8.81</v>
       </c>
-      <c r="I77" s="2">
+      <c r="J77" s="3">
         <v>12.29</v>
       </c>
-      <c r="J77" s="2">
+      <c r="K77" s="3">
         <v>2.78</v>
       </c>
-      <c r="K77" s="2">
+      <c r="L77" s="3">
         <v>1.7</v>
       </c>
-      <c r="L77" s="2">
+      <c r="M77" s="3">
         <v>0.43</v>
       </c>
-      <c r="M77" s="3">
+      <c r="N77" s="2">
         <v>0.99</v>
       </c>
-      <c r="N77" s="3">
+      <c r="O77" s="2">
         <v>0.87</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2BE0B78-315A-B34A-936D-72862B441F7F}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
